--- a/reports/devops-juniors-israel-2026-W21.xlsx
+++ b/reports/devops-juniors-israel-2026-W21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24T09:33:49</t>
+    <t xml:space="preserve">2026-05-24T12:30:07</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -163,423 +163,387 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eitan Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLSTARSIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4413317216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Databases, Virtualization, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eurolaser Technologies Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 2 Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-2-technical-support-at-moon-active-4398349619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-eitan-medical-4407829717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4405967435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLSTARSIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-allstarsit-4410561803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4413611122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
     <t xml:space="preserve">Airobotics</t>
   </si>
   <si>
@@ -604,13 +568,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
   </si>
   <si>
-    <t xml:space="preserve">morning by Green Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -646,28 +610,40 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -676,40 +652,25 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -870,7 +831,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -886,7 +847,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -894,7 +855,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -976,7 +937,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -984,7 +945,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1026,7 +987,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -1137,7 +1098,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>52</v>
@@ -1163,25 +1124,25 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3">
+        <v>71</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3">
-        <v>96</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -1189,31 +1150,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3">
+        <v>57</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3">
-        <v>84</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -1221,31 +1182,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -1253,10 +1214,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>45</v>
@@ -1265,19 +1226,19 @@
         <v>25</v>
       </c>
       <c r="F7" s="3">
+        <v>51</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -1285,31 +1246,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1317,31 +1278,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1349,31 +1310,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1381,28 +1342,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>48</v>
@@ -1413,28 +1374,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>48</v>
@@ -1445,28 +1406,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
@@ -1477,19 +1438,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>101</v>
@@ -1501,7 +1462,7 @@
         <v>102</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -1509,28 +1470,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>48</v>
@@ -1541,28 +1502,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>37</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>44</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
@@ -1573,31 +1534,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>37</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>40</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -1605,19 +1566,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>117</v>
@@ -1629,7 +1590,7 @@
         <v>118</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -1637,19 +1598,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>122</v>
@@ -1661,7 +1622,7 @@
         <v>123</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -1672,10 +1633,10 @@
         <v>124</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -1684,16 +1645,16 @@
         <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
@@ -1701,19 +1662,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>127</v>
@@ -1722,10 +1683,10 @@
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22">
@@ -1733,31 +1694,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
@@ -1765,28 +1726,28 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>27</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>30</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>48</v>
@@ -1797,19 +1758,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="3">
         <v>26</v>
-      </c>
-      <c r="F24" s="3">
-        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>140</v>
@@ -1821,7 +1782,7 @@
         <v>141</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -1829,28 +1790,28 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3">
+        <v>24</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>27</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>48</v>
@@ -1861,31 +1822,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>147</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>148</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1938,7 +1899,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -1953,22 +1914,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2">
@@ -1991,7 +1952,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2020,13 +1981,13 @@
         <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2038,7 +1999,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2049,109 +2010,109 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>71</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="3">
-        <v>96</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K4" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3">
+        <v>57</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3">
-        <v>84</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K5" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K6" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>45</v>
@@ -2160,159 +2121,159 @@
         <v>25</v>
       </c>
       <c r="E7" s="3">
+        <v>51</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K7" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K9" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K10" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>48</v>
@@ -2323,31 +2284,31 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>48</v>
@@ -2358,31 +2319,31 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>48</v>
@@ -2393,25 +2354,25 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2420,39 +2381,39 @@
         <v>102</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="K14" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>40</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>48</v>
@@ -2463,31 +2424,31 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>37</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>44</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>48</v>
@@ -2498,60 +2459,60 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>37</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>40</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K17" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
@@ -2560,33 +2521,33 @@
         <v>118</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="K18" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>122</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
@@ -2595,10 +2556,10 @@
         <v>123</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="K19" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2606,10 +2567,10 @@
         <v>124</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -2618,54 +2579,54 @@
         <v>34</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="K20" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>127</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K21" s="3">
         <v>5</v>
@@ -2673,34 +2634,34 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K22" s="3">
         <v>4</v>
@@ -2708,31 +2669,31 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>30</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>48</v>
@@ -2743,25 +2704,25 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="3">
         <v>26</v>
-      </c>
-      <c r="E24" s="3">
-        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>140</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
@@ -2770,39 +2731,39 @@
         <v>141</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K24" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="3">
+        <v>24</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>48</v>
@@ -2813,66 +2774,66 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>148</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="K26" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>48</v>
@@ -2883,101 +2844,101 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="K28" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="K29" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>48</v>
@@ -2988,69 +2949,69 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>17</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>20</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K31" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>20</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K32" s="3">
         <v>5</v>
@@ -3058,31 +3019,31 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>48</v>
@@ -3093,25 +3054,25 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>184</v>
+        <v>51</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
@@ -3120,119 +3081,14 @@
         <v>186</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="K34" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>17</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K35" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>16</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K36" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K37" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37"/>
+  <autoFilter ref="A1:K34"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3267,9 +3123,6 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3277,11 +3130,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3300,10 +3153,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3311,25 +3164,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3350,178 +3203,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -3541,10 +3394,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
@@ -3552,10 +3405,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
@@ -3563,10 +3416,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4">
@@ -3577,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5">
@@ -3588,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6">
@@ -3599,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3620,13 +3473,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2">
@@ -3637,7 +3490,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3646,22 +3499,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W21.xlsx
+++ b/reports/devops-juniors-israel-2026-W21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="371">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24T12:30:07</t>
+    <t xml:space="preserve">2026-05-24T13:22:48</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -97,12 +97,12 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
@@ -115,6 +115,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -163,6 +166,24 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -181,6 +202,36 @@
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4395489433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
@@ -193,6 +244,39 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-abra-4406502401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4412870787</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -205,6 +289,42 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Student, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Docker, Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-israel-at-algosec-4418656331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-student-at-algosec-4412544220</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAP ECC System Administrator</t>
   </si>
   <si>
@@ -220,147 +340,123 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-eurolaser-technologies-ltd-4407326979</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-wiz-4406744541</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outpost24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal Capital Markets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-21</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4765960101?gh_jid=4765960101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal Capital Markets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-migdal-capital-markets-4414548410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4417361270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Port.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-port-io-4414114905</t>
+    <t xml:space="preserve">Regulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
     <t xml:space="preserve">Global Service Desk Representative</t>
   </si>
   <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
   </si>
   <si>
-    <t xml:space="preserve">Regulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat Karmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-regulus-4404728303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
@@ -388,12 +484,39 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
   </si>
   <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
+  </si>
+  <si>
     <t xml:space="preserve">Menora Mivtachim Group</t>
   </si>
   <si>
@@ -406,12 +529,6 @@
     <t xml:space="preserve">Network Operations Center Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
   </si>
   <si>
@@ -421,9 +538,6 @@
     <t xml:space="preserve">Eitan Medical</t>
   </si>
   <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -433,9 +547,6 @@
     <t xml:space="preserve">AI Bootcamp Course 2</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Git</t>
   </si>
   <si>
@@ -466,24 +577,6 @@
     <t xml:space="preserve">2026-05-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Operations Engineer</t>
   </si>
   <si>
@@ -535,24 +628,9 @@
     <t xml:space="preserve">Augury</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4329813196</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineer IM</t>
   </si>
   <si>
@@ -568,15 +646,375 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
   </si>
   <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4406043821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-help-desk-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4408373512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist- Part Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At-Bay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-part-time-at-at-bay-4399101138</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-evoke-4411433622</t>
+  </si>
+  <si>
     <t xml:space="preserve">Intezer</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
   </si>
   <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-abra-4385901463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gness-4413869359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4671830006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4408229150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 1 Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Auctus Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Ireland, Northern Ireland, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-level-1-help-desk-technician-the-auctus-group-1131916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4413546871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (35746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-35746-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4418664743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4376672023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROOMS by Fattal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-rooms-by-fattal-4404692154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4412906510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architectural intern and personal assistant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oberson Architects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/architectural-intern-and-personal-assistant-at-oberson-architects-4411144727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online Hotel Booker No Experience Needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aisle and Abroad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York, New York, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-online-hotel-booker-no-experience-needed-aisle-and-abroad-1131707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online Booking &amp;amp; Reservations Assistant No Experience Needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, Boston, Kentucky, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-online-booking-amp-reservations-assistant-no-experience-needed-aisle-and-abroad-1131698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booking Coordinator No Experience Needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-booking-coordinator-no-experience-needed-aisle-and-abroad-1131708</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -586,9 +1024,6 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
@@ -610,58 +1045,52 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -670,9 +1099,6 @@
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -685,12 +1111,12 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
@@ -701,12 +1127,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -831,7 +1251,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -839,7 +1259,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -847,7 +1267,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -855,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>68</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -937,7 +1357,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -945,7 +1365,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -953,7 +1373,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -987,7 +1407,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -995,7 +1415,15 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>5</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1019,34 +1447,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1054,31 +1482,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1086,31 +1514,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1118,31 +1546,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1150,31 +1578,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -1182,31 +1610,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -1214,31 +1642,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -1246,31 +1674,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
@@ -1278,31 +1706,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -1310,19 +1738,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>85</v>
@@ -1334,7 +1762,7 @@
         <v>86</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -1348,25 +1776,25 @@
         <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3">
+        <v>57</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1374,19 +1802,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>94</v>
@@ -1398,7 +1826,7 @@
         <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -1412,25 +1840,25 @@
         <v>97</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1438,22 +1866,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -1462,7 +1890,7 @@
         <v>102</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -1470,31 +1898,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1502,31 +1930,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1534,31 +1962,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1566,31 +1994,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -1598,31 +2026,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -1630,31 +2058,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -1662,31 +2090,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>40</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3">
-        <v>32</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="22">
@@ -1694,31 +2122,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23">
@@ -1726,31 +2154,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
@@ -1758,31 +2186,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
@@ -1790,31 +2218,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -1822,31 +2250,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1886,7 +2314,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1899,69 +2327,69 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
         <v>9</v>
@@ -1969,270 +2397,270 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K5" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K6" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="K7" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K8" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K9" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2241,10 +2669,10 @@
         <v>86</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K10" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2255,28 +2683,28 @@
         <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="3">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
         <v>9</v>
@@ -2284,25 +2712,25 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
@@ -2311,10 +2739,10 @@
         <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K12" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2325,54 +2753,54 @@
         <v>97</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K13" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2381,42 +2809,42 @@
         <v>102</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="K14" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K15" s="3">
         <v>9</v>
@@ -2424,34 +2852,34 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K16" s="3">
         <v>9</v>
@@ -2459,69 +2887,69 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="K17" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" s="3">
         <v>9</v>
@@ -2529,209 +2957,209 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="K19" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="K20" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>40</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="3">
-        <v>32</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="K21" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="K22" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="K23" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K24" s="3">
         <v>9</v>
@@ -2739,34 +3167,34 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" s="3">
         <v>9</v>
@@ -2774,139 +3202,139 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="K26" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="K27" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K28" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="K29" s="3">
         <v>5</v>
@@ -2914,95 +3342,95 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K30" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>173</v>
+        <v>69</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="3">
+        <v>26</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>17</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="G32" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
@@ -3011,42 +3439,42 @@
         <v>178</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="K32" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K33" s="3">
         <v>9</v>
@@ -3054,41 +3482,1571 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>23</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
+      <c r="J34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K34" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K35" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>20</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>20</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K37" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>20</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K38" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>17</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>16</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K40" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="3">
         <v>13</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K34" s="3">
+      <c r="F41" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="3">
+        <v>13</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>13</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="3">
+        <v>13</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>13</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K46" s="3">
         <v>4</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="3">
+        <v>10</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>10</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="3">
+        <v>8</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="3">
+        <v>8</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="3">
+        <v>4</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="3">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K78" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K78"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3123,6 +5081,50 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
+    <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
+    <hyperlink ref="I37" r:id="rId36"/>
+    <hyperlink ref="I38" r:id="rId37"/>
+    <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
+    <hyperlink ref="I46" r:id="rId45"/>
+    <hyperlink ref="I47" r:id="rId46"/>
+    <hyperlink ref="I48" r:id="rId47"/>
+    <hyperlink ref="I49" r:id="rId48"/>
+    <hyperlink ref="I50" r:id="rId49"/>
+    <hyperlink ref="I51" r:id="rId50"/>
+    <hyperlink ref="I52" r:id="rId51"/>
+    <hyperlink ref="I53" r:id="rId52"/>
+    <hyperlink ref="I54" r:id="rId53"/>
+    <hyperlink ref="I55" r:id="rId54"/>
+    <hyperlink ref="I56" r:id="rId55"/>
+    <hyperlink ref="I57" r:id="rId56"/>
+    <hyperlink ref="I58" r:id="rId57"/>
+    <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3130,65 +5132,1087 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
+        <v>100</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3">
+        <v>74</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3">
+        <v>70</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
         <v>17</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>175</v>
+      <c r="E8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="3">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="3">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="3">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="3">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="3">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="3">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="3">
+        <v>6</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="3">
+        <v>6</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="3">
+        <v>6</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="3">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="3">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="3">
+        <v>6</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="3">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="3">
+        <v>4</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="3">
+        <v>3</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="3">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="3">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="3">
+        <v>3</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="3">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="3">
+        <v>3</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="3">
+        <v>3</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="3">
+        <v>3</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="3">
+        <v>3</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="3">
+        <v>3</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G45"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
+    <hyperlink ref="F14" r:id="rId13"/>
+    <hyperlink ref="F15" r:id="rId14"/>
+    <hyperlink ref="F16" r:id="rId15"/>
+    <hyperlink ref="F17" r:id="rId16"/>
+    <hyperlink ref="F18" r:id="rId17"/>
+    <hyperlink ref="F19" r:id="rId18"/>
+    <hyperlink ref="F20" r:id="rId19"/>
+    <hyperlink ref="F21" r:id="rId20"/>
+    <hyperlink ref="F22" r:id="rId21"/>
+    <hyperlink ref="F23" r:id="rId22"/>
+    <hyperlink ref="F24" r:id="rId23"/>
+    <hyperlink ref="F25" r:id="rId24"/>
+    <hyperlink ref="F26" r:id="rId25"/>
+    <hyperlink ref="F27" r:id="rId26"/>
+    <hyperlink ref="F28" r:id="rId27"/>
+    <hyperlink ref="F29" r:id="rId28"/>
+    <hyperlink ref="F30" r:id="rId29"/>
+    <hyperlink ref="F31" r:id="rId30"/>
+    <hyperlink ref="F32" r:id="rId31"/>
+    <hyperlink ref="F33" r:id="rId32"/>
+    <hyperlink ref="F34" r:id="rId33"/>
+    <hyperlink ref="F35" r:id="rId34"/>
+    <hyperlink ref="F36" r:id="rId35"/>
+    <hyperlink ref="F37" r:id="rId36"/>
+    <hyperlink ref="F38" r:id="rId37"/>
+    <hyperlink ref="F39" r:id="rId38"/>
+    <hyperlink ref="F40" r:id="rId39"/>
+    <hyperlink ref="F41" r:id="rId40"/>
+    <hyperlink ref="F42" r:id="rId41"/>
+    <hyperlink ref="F43" r:id="rId42"/>
+    <hyperlink ref="F44" r:id="rId43"/>
+    <hyperlink ref="F45" r:id="rId44"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3203,178 +6227,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>333</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>334</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>190</v>
+        <v>294</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>191</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>194</v>
+        <v>339</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>196</v>
+        <v>341</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>197</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>198</v>
+        <v>285</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>199</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>201</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>203</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>204</v>
+        <v>346</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>205</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>207</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>208</v>
+        <v>349</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>209</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>210</v>
+        <v>351</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>212</v>
+        <v>353</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>213</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>214</v>
+        <v>355</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>215</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>217</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>218</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>213</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3391,13 +6415,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
@@ -3405,10 +6429,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">
@@ -3416,10 +6440,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4">
@@ -3427,10 +6451,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5">
@@ -3441,7 +6465,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>224</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6">
@@ -3452,7 +6476,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>225</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -3470,16 +6494,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>369</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>228</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
@@ -3487,10 +6511,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3499,22 +6523,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>230</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="D4" s="3"/>
     </row>
